--- a/app/udp_tool/output_excel_reports/pdm/05_Carbon_Calculator_UDP_Comparison.xlsx
+++ b/app/udp_tool/output_excel_reports/pdm/05_Carbon_Calculator_UDP_Comparison.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDP Comparison" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By UDP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnostics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="UDP Comparison" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="By UDP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Diagnostics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UDP Comparison'!$A$1:$H$1</definedName>
@@ -122,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,6 +148,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -549,7 +552,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-09-03 10:50:57</t>
+          <t>2026-09-04 19:47:06</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr"/>
@@ -588,7 +591,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>c:\Users\SrinivasaPesala\Desktop\migration-platform_v004\app\udp_tool\input_sap_models\05_Carbon_Calculator.pdm</t>
+          <t>C:\Users\Shivansh\Downloads\migration-platform_4_sept_final\sappdmodels\pdm\05_Carbon_Calculator.pdm</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr"/>
@@ -601,7 +604,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>c:\Users\SrinivasaPesala\Desktop\migration-platform_v004\app\udp_tool\output_erwin_models\05_Carbon_Calculator.erwin</t>
+          <t>app\udp_tool\output_erwin_models\05_Carbon_Calculator.erwin</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr"/>
@@ -614,7 +617,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>com</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -60778,7 +60781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -60801,7 +60804,7 @@
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>c:\Users\SrinivasaPesala\Desktop\migration-platform_v004\app\udp_tool\output_erwin_models\05_Carbon_Calculator.erwin</t>
+          <t>app\udp_tool\output_erwin_models\05_Carbon_Calculator.erwin</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr"/>
@@ -60814,7 +60817,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>com</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -60843,72 +60846,100 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Objects read from erwin</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="n">
-        <v>101</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr"/>
+          <t>Decoder self-test</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Share of decoded values that pair with a source value. A low score means the property slot mapping is wrong for this erwin build, not that the data is wrong.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>Objects read from erwin</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>101</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
           <t>UDP values read from erwin</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
-        <v>1581</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B7" s="14" t="n">
+        <v>1591</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Readback notes</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr"/>
+      <c r="C9" s="17" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Read 1581 UDP value(s) from erwin via SCAPI.</t>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Fell back to the offline decoder (pywin32 is not installed, so erwin cannot be queried (No module named 'pythoncom'). Use --readback binary for an offline cross-check.)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Decoder self-test: 1591/1591 paired values agree (100.0%); slot mapping confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Source data warnings</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr"/>
-      <c r="C11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr"/>
+      <c r="C13" s="17" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/app/udp_tool/output_excel_reports/pdm/05_Carbon_Calculator_UDP_Comparison.xlsx
+++ b/app/udp_tool/output_excel_reports/pdm/05_Carbon_Calculator_UDP_Comparison.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDP Comparison" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By UDP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnostics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="UDP Comparison" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="By UDP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Diagnostics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UDP Comparison'!$A$1:$H$1</definedName>
@@ -555,7 +555,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-09-05 21:17:08</t>
+          <t>2026-09-05 20:23:45</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\SrinivasaPesala\Desktop\migration-platform_4_sept_final_h_l_m\sappdmodels\pdm\05_Carbon_Calculator.pdm</t>
+          <t>C:\Users\Shivansh\Downloads\migration-platform_4_sept_final\sappdmodels\pdm\05_Carbon_Calculator.pdm</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr"/>
